--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP)</t>
+          <t>Senior BackEnd Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1224b5cebc9ca8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc3a06012f008f3</t>
+          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior BackEnd Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,42 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, RDS, Databricks, Scala, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d1e17a962b5fca</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,199 +1161,199 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>AI Tech Partner (USA)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73966b170bd92bef</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>AI Tech Partner (USA)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f328d78d7b80a9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>AI Tech Partner (USA)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19cd66b829b5339a</t>
+          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a15946806730eb5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21a5637c26aeee6</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18d46da9a88bc799</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ea1b73fd02e910</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520267b51ab833b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>API Security Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,19 +2141,19 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7540039fe27c9ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QA Automation Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, SQL Server, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a8c0b028e6bca22</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Integrations Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bb4373ad110466f</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Integrations Architect</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vista Higher Learning</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c4f04946a604d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,59 +2526,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Database Engineer with Java MS</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25b94269754a9820</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>ARIES SOLUTIONS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,104 +2831,104 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, ELT, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=545ade558773e3d3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>Distinguished Architect, Data Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,24 +3146,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - ML Platform</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f38667e23fc2e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Administration &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Engineer -.NET</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,120 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior BI Specialist – R01562930</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
@@ -923,42 +923,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>AI Tech Partner (USA)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
+          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Tech Partner (USA)</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,52 +1291,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
@@ -1728,25 +1728,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Snowflake, Power BI</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>MOHELA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Senior Endpoint Security Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,17 +3146,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Azure, GCP, BigQuery, Spark, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=d47d7a74b3089448</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Venatore</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Fort Belvoir, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, PostgreSQL, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=ff27edbece16f3be</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer -.NET</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a13dd69a11dd2a2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Tech Partner (USA)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
+          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
+          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>AI Tech Partner (USA)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,52 +1291,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect (Datastage, DBT, ETL, SSIS) – R01562351</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Oracle, SQL Server, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=518471bf55b68ee3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ARIES SOLUTIONS</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,77 +2831,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ELT, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545ade558773e3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MOHELA</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hive, Impala, Spark, Scala, Data Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00ea21484fff4c0b</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,627 +2911,627 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=ab1065855ef14eca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=71636389aa78efd5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fef5e8073cb383</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=9501ebd5923f67aa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
+          <t>https://www.indeed.com/viewjob?jk=388ad3c9fba9271c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=d322c261386f56e2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Endpoint Security Engineer - Global Security Organization</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47d7a74b3089448</t>
+          <t>https://www.indeed.com/viewjob?jk=a5a0764074fe0317</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=ae8bb13382eba565</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=df0d7a279864544b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=06051094e158c2ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=d1cdb70fd9c89334</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed9fd91845c56f2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=c84ed7edd2463130</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5ce47ffa4f81f6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=549bc9397ed63a24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbf07a1b9a86669</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>NinjaOne</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=af98402106d5d501</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>ARIES SOLUTIONS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, ELT, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=545ade558773e3d3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INTRAFI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aab0d4e5d8dae5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,15 +3628,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea1ea320a3da1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Administration &amp; Infrastructure</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
+          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cognos Optimization Specialist</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Venatore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Belvoir, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, PostgreSQL, ETL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff27edbece16f3be</t>
+          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Endpoint Security Engineer - Global Security Organization</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=d47d7a74b3089448</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,15 +4126,680 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Engineer II-Software Development</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Super Micro Computer, Inc.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Technical Architect</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>INTRAFI</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aab0d4e5d8dae5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fea1ea320a3da1b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Administration &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Venatore</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fort Belvoir, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, PostgreSQL, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff27edbece16f3be</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>WellRithms</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Software Application Developer, IT</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Centurion Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sterling, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Analytics Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Tampa Electric Company</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Relias</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>BI Developer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>S&amp;O Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior BI Specialist – R01562930</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Tech Partner (USA)</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,112 +1221,112 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc2a5a288d17425</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Tech Partner (USA)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ff85dd600047b4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Tech Partner (USA)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eccc725fef05e64</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Architect (Datastage, DBT, ETL, SSIS) – R01562351</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Time Travel, Oracle, SQL Server, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=518471bf55b68ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,77 +2271,77 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, ELT, dbt, MLOps</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,129 +2761,129 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,15 +2893,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,404 +2911,404 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab1065855ef14eca</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71636389aa78efd5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fef5e8073cb383</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9501ebd5923f67aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388ad3c9fba9271c</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d322c261386f56e2</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a0764074fe0317</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae8bb13382eba565</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0d7a279864544b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06051094e158c2ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1cdb70fd9c89334</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3317,103 +3317,103 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed9fd91845c56f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c84ed7edd2463130</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5ce47ffa4f81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3422,116 +3422,116 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=549bc9397ed63a24</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bbf07a1b9a86669</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NinjaOne</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Scala, NoSQL, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af98402106d5d501</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ARIES SOLUTIONS</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ELT, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=545ade558773e3d3</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,15 +3593,15 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,15 +3628,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6958a876172ec730</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cognos Optimization Specialist</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Databricks, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39930f1669a9c233</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Endpoint Security Engineer - Global Security Organization</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Spark Streaming, Kafka, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3820,986 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d47d7a74b3089448</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Intern: Financial Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>EquipmentShare</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Columbia, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Cloudera</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Hilcorp Energy Company</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>EDB</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Engineer II-Software Development</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Microchip Technology</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Super Micro Computer, Inc.</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Technical Architect</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>INTRAFI</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Oracle, DynamoDB, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aab0d4e5d8dae5bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Administration &amp; Infrastructure</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fea1ea320a3da1b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Administration &amp; Infrastructure</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>OR, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6596f101bae22a82</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Venatore</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Fort Belvoir, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, PostgreSQL, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff27edbece16f3be</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>WellRithms</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Data Analytics Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Tampa Electric Company</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Relias</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, Kafka, Data Modeling, ELT</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, BigQuery, Hive, Spark, PySpark, Scala, Kafka, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=799dc2ba53bfb669</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,42 +1991,42 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3785,41 +3785,6 @@
         </is>
       </c>
       <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,69 +2656,69 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3750,41 +3750,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior BackEnd Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python and PySpark, No SQL Developer-2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-2</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Insurance Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74923e4619f29cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,76 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Cloudera Context Search Team</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Cloudera</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,15 +3671,50 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior BI Specialist – R01562930</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Brillio LLC</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Grata</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Prudential</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, RDS, Scala, MySQL, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=7f151ec7568ba313</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,29 +1886,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Databricks Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
@@ -2603,52 +2603,52 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloudera Context Search Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cloudera</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kubernetes, AKS</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cc5ba5bc4131e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,52 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Event Hubs, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ae0639bcc380726</t>
+          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f3d707966b2b604</t>
+          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer (Containers Focus)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Viasat</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Indev</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
         </is>
       </c>
     </row>
@@ -888,52 +888,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a19064215d6504dc</t>
+          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2384362c47d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Prudential</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Scala, MySQL, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f151ec7568ba313</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Databricks Automation Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alderwood of North Carolina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c263ee15c9d7ff4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=816e3ba22947d18d</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,164 +2446,164 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,15 +2613,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,190 +3496,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior BI Specialist – R01562930</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Virginia Beach, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python and PySpark, No SQL Developer-2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indev</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beb67bf43c44dfc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-2</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b7a6f9f89825521</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Azure, Databricks, Blob Storage, Cloud Storage, Hadoop, HDFS, Hive</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68341534918cf2bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22742d685387c57f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Insurance Integration Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Blob Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7effb39eab56def</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Grata</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=631f60bd15f1b3d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,112 +1781,112 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,77 +1956,77 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alderwood of North Carolina</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f6b4e41cc2869d</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Archdiocese of Chicago</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Expressable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Founding Backend Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Clipbook</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Application Developer, IT</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Centurion Health</t>
+          <t>WellRithms</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
+          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>Software Application Developer, IT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Centurion Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
+          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Data Analytics Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>S&amp;O Developer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>S&amp;O Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior BI Specialist – R01562930</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
         </is>
       </c>
     </row>
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,15 +3496,50 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,60 +643,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers Focus)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, HBase, Impala, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131b0feaf824cce9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python and PySpark, No SQL Developer-2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-2</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer - AML &amp; Financial Crimes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wando, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Data Engineer, Global Credit Technology</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>The Carlyle Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158d4d251d7cfe41</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ingram Content Group</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>La Vergne, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Big Data</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Archdiocese of Chicago</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, Star Schema, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b260063a1f060a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
+          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software &amp; Electronics Development Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Digital Dynamics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scotts Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expressable</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,42 +2376,42 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expressable</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Application Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VASS Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,59 +2701,59 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Data Engineer (*Grant Funded)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>River, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior BI Specialist – R01562930</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5053e60f58006ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,50 +3496,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, IAM, RDS, Spark</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Python and PySpark, No SQL Developer-2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-2</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,112 +976,112 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETL Developer - AML &amp; Financial Crimes</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f8ec969f3563e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ae67c62e9e932e</t>
+          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wando, SC, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer, Global Credit Technology</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Carlyle Group</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,77 +1396,77 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
@@ -1728,25 +1728,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef074d74f0c7a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a7b790a520c25c</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Big Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365b2385af6a0f99</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Cloud Systems Architect - Cloud ERP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Celsius Network</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e6afce3c14c5e32</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software &amp; Electronics Development Engineer II</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Digital Dynamics</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Scotts Valley, CA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=174e2731cd487355</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expressable</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expressable</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Application Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>VASS Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,104 +2621,104 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Snowflake, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca736b058903f7a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VASS Inc</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c682a9d6efe9dcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (*Grant Funded)</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ann &amp; Robert H. Lurie Children's Hospital of Chicago</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>River, IL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be4284919556a7f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94129ba3e4c3efdc</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Hilcorp Energy Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Founding Backend Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Clipbook</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Founding Backend Engineer – AI &amp; Data</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Clipbook</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,322 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb1e4c91a109f193</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22cae783634b6fb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Software Application Developer, IT</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Centurion Health</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Sterling, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, Pentaho, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b9a649df292057</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Data Analytics Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tampa Electric Company</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, dbt</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84060e304bd5181b</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>S&amp;O Developer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ExxonMobil</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd099c12f1c683af</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Payments Engineer Specialist – DataStage Cloud Technologies</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Blob Storage, Hadoop, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa8c98195ac4096</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I (Snowflake)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ingram Content Group</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Vergne, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,59 +1896,59 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Cloud Systems Architect - Cloud ERP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Celsius Network</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Systems Architect - Cloud ERP</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Celsius Network</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Expressable</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expressable</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>VASS Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VASS Inc</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Berkley</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manassas, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, PostgreSQL, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6b2c708f3ef80c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Berkley</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Manassas, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, HBase, YARN, Impala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154e5228cf0e30aa</t>
+          <t>https://www.indeed.com/viewjob?jk=88146716ceed528b</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Forward Deploy Data Engineer-Associate</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a094400a036939</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Forward Deploy Data Engineer-Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Veritone</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Data Lake Storage, Blob Storage, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
+          <t>https://www.indeed.com/viewjob?jk=34525f4e47bd513d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product Support &amp; Platform Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Univerus</t>
+          <t>Veritone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
+          <t>https://www.indeed.com/viewjob?jk=42442aa4f1f05e8b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Product Support &amp; Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Univerus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
+          <t>https://www.indeed.com/viewjob?jk=1812ab21ac264af8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snowflake Engineer (Datastage, SSIS, DB2, ETL) – R01562352</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, GCP, Snowflake, Time Travel, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5818d3536fb861</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IS Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=a92d3aa09f2f357e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Great value staffing and technologies.inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>Ronin Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>EMR, Azure, Data Factory, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=00d9114936398c43</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala, MLOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,112 +1396,112 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,164 +1686,164 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=fedbff1fa3c408c5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer I (Snowflake)</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4860f5d8874039e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ingram Content Group</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>La Vergne, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
@@ -1978,117 +1978,117 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Systems Architect - Cloud ERP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Celsius Network</t>
+          <t>Wahoo Fitness</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
+          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+          <t>Cloud Systems Architect - Cloud ERP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expressable</t>
+          <t>Celsius Network</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data and BI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Food &amp; Vending</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>dbt Engineer II or III</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,94 +2421,94 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Analytics Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lockton Companies</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Expressable</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineering &amp; Integration</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VASS Inc</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oran Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>Data Engineering &amp; Integration</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,77 +2806,77 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>AI Enterprise Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
+          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data and BI Solutions Developer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ExtraMile</t>
+          <t>VASS Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hilcorp Energy Company</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Founding Backend Engineer – AI &amp; Data</t>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Clipbook</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2d6ac7747d0244</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba1b325ba28e7e98</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,295 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Hilcorp Energy Company</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Proactive Logic Consulting Inc</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Founding Backend Engineer – AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Clipbook</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Founding Data Engineer (Core Data Platform)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Embedding VC</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Somerville, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,52 +1028,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IS Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92d3aa09f2f357e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Great value staffing and technologies.inc</t>
+          <t>Ronin Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>EMR, Azure, Data Factory, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd57aeb1d54c26e</t>
+          <t>https://www.indeed.com/viewjob?jk=00d9114936398c43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ronin Consulting</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d9114936398c43</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4c458ab00e0053aa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Bandwidth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer- Java- Big Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Blue Cross and Blue Shield of Kansas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=fedbff1fa3c408c5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedbff1fa3c408c5</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
@@ -1798,52 +1798,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Ingram Content Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>La Vergne, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ingram Content Group</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>La Vergne, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Systems Architect - Cloud ERP</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Celsius Network</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
+          <t>https://www.indeed.com/viewjob?jk=da47b75bd94fdaab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud Systems Architect - Cloud ERP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Celsius Network</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Data Analyst / Data Engineer - 100% Remote</t>
+          <t>Associate Network Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expressable</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, ETL, ELT, dbt, CI/CD, GitHub Actions, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b43a6238c24521c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CLASP</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Developer Advocate - Data Observability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
@@ -2883,25 +2883,25 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2d6ac7747d0244</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
+          <t>Senior Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Proactive Logic Consulting Inc</t>
+          <t>Cinch Home Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Redshift, RDS, Kafka, Snowflake, Oracle, Talend, Power BI, Tableau, MicroStrategy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
+          <t>https://www.indeed.com/viewjob?jk=688419cc363c7dc5</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Founding Backend Engineer – AI &amp; Data</t>
+          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Clipbook</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
+          <t>Founding Backend Engineer – AI &amp; Data</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Embedding VC</t>
+          <t>Clipbook</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
+          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd2d6ac7747d0244</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cognos Business Intelligence Analyst</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cognos Business Intelligence Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,15 +3461,85 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>

--- a/results/job_matches_2026-03-26.xlsx
+++ b/results/job_matches_2026-03-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Back-end Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inter Miami CF</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cb212e78f495655</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-2</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Inter Miami CF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, ECS, IAM, Scala, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5ca26ba048f780</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4ec2058b64c4b8</t>
         </is>
       </c>
     </row>
@@ -818,60 +818,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Snowflake Engineer II or III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a620b68dc800c0</t>
+          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snowflake Engineer II or III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross of Idaho</t>
+          <t>Blueprint Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meridian, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Time Travel, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c5c99f1f2788d8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Air Methods</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad28ed59ecf58e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,42 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d882b1b6e861b73</t>
+          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
         </is>
       </c>
     </row>
@@ -998,55 +998,55 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blueprint Technologies</t>
+          <t>Robert E. Mason &amp; Associates</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf248a552a2b9944</t>
+          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>The Clorox Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d2aa11942c20e</t>
+          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>CloudOps Engineer - Evinova</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ronin Consulting</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EMR, Azure, Data Factory, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00d9114936398c43</t>
+          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=305629713c8cf97d</t>
+          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>BridgeNexus Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=054e907298f72492</t>
+          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Robert E. Mason &amp; Associates</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, Hadoop, Spark, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734589cead82347f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
         </is>
       </c>
     </row>
@@ -1208,20 +1208,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Clorox Company</t>
+          <t>D.A. Davidson Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b00f8471e050b5f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CloudOps Engineer - Evinova</t>
+          <t>Database Administrator (Microsoft SQL, Azure SQL, Snowflake, Microsoft Fabric, Azure DevOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Guggenheim Partners</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, MySQL, MongoDB, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7fe2318ed9385f4</t>
+          <t>https://www.indeed.com/viewjob?jk=242a3be422a3c7a1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c458ab00e0053aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f56bdac321f08c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218e42d5335a326d</t>
+          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr AWS Data Engineer - Export Control (only Citizen and GC)</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cad185c5c326ba55</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Software Engineer Sr Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BridgeNexus Technologies Inc</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a41cd00b4d0c37b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Science/MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Oracle, ETL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e90b52e3a1a17a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaac56b41d3197f1</t>
+          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Java- Big Data</t>
+          <t>Senior Data Platform Integration Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Integral Ad Science</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Databricks, Spark, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beb81df979d35f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D.A. Davidson Companies</t>
+          <t>Pavion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f829d868d8f7d81e</t>
+          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Software Engineer - Hybrid/Bellevue, WA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Brook Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d2d78dceeadfde</t>
+          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Kansas</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedbff1fa3c408c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5560c25882ca2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Create Music Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5132b666e5ec7b</t>
+          <t>https://www.indeed.com/viewjob?jk=758c67189c730321</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Scientist, Cat Foresight</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,84 +1721,84 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928956c2a29e11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>Asahi Kasei</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e271eca1a4159</t>
+          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>aPriori Technologies Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Concord, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b502ed0e95608acf</t>
+          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Science/MLOps Engineer</t>
+          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,15 +1808,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bc0880e6a383b9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609352d6a96dfbb8</t>
+          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Platform Integration Engineer</t>
+          <t>Senior DevSecOps and Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Akira Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Spark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f4676b6700d720</t>
+          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pavion</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Glue, S3, RDS, Azure, Blob Storage, Cloud Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b65884a2def3e0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ingram Content Group</t>
+          <t>Nimbus Cloud Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La Vergne, TN, US USA</t>
+          <t>Plymouth, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, Docker</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f85867189225f16</t>
+          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Cat Foresight</t>
+          <t>Senior Data Engineer - Information Technology</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Cache Creek Casino Resort</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Brooks, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Power BI, Tableau, MLOps, CI/CD, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7bbb7516c97c777</t>
+          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Hybrid/Bellevue, WA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brook Inc.</t>
+          <t>CLASP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=442324d7b318c1db</t>
+          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Asahi Kasei</t>
+          <t>Xbow</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Databricks, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64935dc6687cef43</t>
+          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data and BI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wahoo Fitness</t>
+          <t>American Food &amp; Vending</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, BigQuery, Snowflake, MongoDB, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c17cf51303d69c</t>
+          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>dbt Engineer II or III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>aPriori Technologies Inc</t>
+          <t>Blue Cross of Idaho</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concord, MA, US USA</t>
+          <t>Meridian, ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daac76271abc94d6</t>
+          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer – MVA Inference &amp; Audience Development (Remote, Global)</t>
+          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1da64f371c44744</t>
+          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Lockton Companies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04361f4ee433abc8</t>
+          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior DevSecOps and Infrastructure Engineer</t>
+          <t>Senior Developer Advocate - Data Observability</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Akira Technologies</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c475c8fe9ed280d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI DevOps and Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crowe LLP</t>
+          <t>COGNWIZ SOLUTIONS LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Senior Data Engineer – Snowflake Migration</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Oran Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da47b75bd94fdaab</t>
+          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Systems Architect - Cloud ERP</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Celsius Network</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Spark, Scala, SQL Server, Data Modeling, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7563ac0384623a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e610dde5567f71</t>
+          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f902a4bcfd6f0dc</t>
+          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nimbus Cloud Solutions</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plymouth, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bf60a25aee7ba1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Network Security Engineer</t>
+          <t>Data and BI Solutions Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ExtraMile</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Information Technology</t>
+          <t>Founding Data Engineer (Core Data Platform)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cache Creek Casino Resort</t>
+          <t>Embedding VC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brooks, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,1022 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ca3b7bd8d76f7e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>CLASP</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, BigQuery, Scala, Snowflake, PostgreSQL, NoSQL, dbt, Tableau, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9063dc15527a3f25</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Xbow</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, PostgreSQL, Terraform, Kubernetes, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e013910d7dfe6dce</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Data and BI Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>American Food &amp; Vending</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=715e9e79d209ba09</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>dbt Engineer II or III</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Blue Cross of Idaho</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Meridian, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Scala, Snowflake, Data Modeling, Kimball, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af151db159b7fdc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>PPCO Data Analytics – Systems &amp; Data Analytics</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Warren, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3577fd017ba1e45</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Sr Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Lockton Companies</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Databricks, Spark, Scala, Dimensional Modeling, Power BI, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c80a21add211681e</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Engineering &amp; Integration</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Data Engineering &amp; Integration</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Hadoop, Scala, Snowflake, Data Modeling, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>AI Enterprise Architect</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Peloton</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=337e4082664be656</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>VASS Inc</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7ebd826073989c</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Senior Developer Advocate - Data Observability</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc015d21fb039200</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>COGNWIZ SOLUTIONS LLC</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, HBase, Spark, Kafka, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9f79c9da6376568</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Engineer II-Software Development</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Microchip Technology</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b9464571ec4a13</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Snowflake Migration</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Oran Inc</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, ETL, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94f36c91f8b842d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf05ce0c2fca8aa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=763e204d324d6943</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09de6be18461fa65</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cd71d5dc3f6911a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Data and BI Solutions Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ExtraMile</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>FL, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5810d2049fbe45</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Hilcorp Energy Company</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Cinch Home Services</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Kafka, Snowflake, Oracle, Talend, Power BI, Tableau, MicroStrategy</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=688419cc363c7dc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Fractional SQL Server &amp; PostgreSQL DBA Consultant (AI-Forward)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Proactive Logic Consulting Inc</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb428f27c27f9ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Founding Backend Engineer – AI &amp; Data</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Clipbook</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22ee1aa79e315b8e</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd2d6ac7747d0244</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Founding Data Engineer (Core Data Platform)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Embedding VC</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1ad745848a72d300</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Business Intelligence Developer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Somerville, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, SQL Server, MySQL, Dimensional Modeling, ETL, Talend, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d53ca27d22c29c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cognos Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Crowe LLP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Sarasota, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
